--- a/output/AEL-Verrechnung.xlsx
+++ b/output/AEL-Verrechnung.xlsx
@@ -1,110 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dbsw-my.sharepoint.com/personal/dennis_heinze_deutschebahn_com/Documents/Desktop/Python/BetraBuilder/output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_0A5AD0775170BE6EE87450B44BEE263DE0A1D991" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCBD6FA-C5F2-4F75-9A9A-83753174DDDE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AEL-Aufträge" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEL-Aufträge" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Auftragsart</t>
-  </si>
-  <si>
-    <t>Eckstarttermin</t>
-  </si>
-  <si>
-    <t>Eckendtermin</t>
-  </si>
-  <si>
-    <t>AAR-ProjektNr</t>
-  </si>
-  <si>
-    <t>Kurztext</t>
-  </si>
-  <si>
-    <t>Verantw.ArbPl.</t>
-  </si>
-  <si>
-    <t>Auftrag</t>
-  </si>
-  <si>
-    <t>AAR-Auftr.-Nr.</t>
-  </si>
-  <si>
-    <t>(Buchungsdatum)
-Datum</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Arbeitsplatz (A0BBK, A0BETRA oder A0SIPLA)</t>
-  </si>
-  <si>
-    <t>(LArt)
-FAA
-(immer 1065)</t>
-  </si>
-  <si>
-    <t>Werk
-(immer 16ES)</t>
-  </si>
-  <si>
-    <t>Einheit
-(immer MIN)</t>
-  </si>
-  <si>
-    <t>(Ist-Arbeit)
-Menge</t>
-  </si>
-  <si>
-    <t>(Rückmeldetext)
-Tätigkeitsbezeichnung/Betra-Nr./SiPla-Nr.</t>
-  </si>
-  <si>
-    <t>Bemerkung / Frage</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="DB Neo Office Head"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="DB Neo Office Head"/>
     </font>
     <font>
+      <name val="Db Neo Office"/>
       <sz val="11"/>
-      <name val="Db Neo Office"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -121,8 +53,14 @@
         <bgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,34 +83,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -460,100 +475,301 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.5703125" customWidth="1"/>
+    <col width="13" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
+    <col width="16" customWidth="1" style="6" min="2" max="2"/>
+    <col width="14" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="15" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10" customWidth="1" style="6" min="5" max="5"/>
+    <col width="16" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
+    <col width="10" customWidth="1" style="6" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="6" min="8" max="8"/>
+    <col width="17" customWidth="1" style="6" min="9" max="9"/>
+    <col width="10" customWidth="1" style="6" min="10" max="10"/>
+    <col width="44" bestFit="1" customWidth="1" style="6" min="11" max="11"/>
+    <col width="14" customWidth="1" style="6" min="12" max="13"/>
+    <col width="14" customWidth="1" style="6" min="13" max="13"/>
+    <col width="13" bestFit="1" customWidth="1" style="6" min="14" max="14"/>
+    <col width="14" bestFit="1" customWidth="1" style="6" min="15" max="15"/>
+    <col width="43" bestFit="1" customWidth="1" style="6" min="16" max="16"/>
+    <col width="19" customWidth="1" style="6" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="57" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
+    <row r="1" ht="57" customHeight="1" s="6">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Auftragsart</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Eckstarttermin</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Eckendtermin</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>AAR-ProjektNr</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Kurztext</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Verantw.ArbPl.</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Auftrag</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>AAR-Auftr.-Nr.</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>(Buchungsdatum)
+Datum</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitsplatz (A0BBK, A0BETRA oder A0SIPLA)</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>(LArt)
+FAA
+(immer 1065)</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Werk
+(immer 16ES)</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Einheit
+(immer MIN)</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>(Ist-Arbeit)
+Menge</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>(Rückmeldetext)
+Tätigkeitsbezeichnung/Betra-Nr./SiPla-Nr.</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bemerkung / Frage</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+    </row>
+    <row r="3" s="6">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+    </row>
+    <row r="4" s="6">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>26.11.2025</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Heinze</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>A0BETRA</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>16ES</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Betra F33 1234-26</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>cvncvn</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>dbhh</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>26.11.2025</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Heinze</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>A0BETRA</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>16ES</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>Betra F33 2345-26</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>nnv</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
